--- a/out/Attention-S4_repeat_1_000001.xlsx
+++ b/out/Attention-S4_repeat_1_000001.xlsx
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.809276425334539</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4257236973058409</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1742763026941591</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1742763026941591</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1742763026941591</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1742763026941591</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1742763026941591</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1742763026941591</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.809276425334539</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.809276425334539</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1742763026941591</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.809276425334539</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1742763026941591</v>
+        <v>4.409276425334538</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.1769695850834732</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC43" t="n">
-        <v>-8.576601622242015e-05</v>
+        <v>-3.654061715502758e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03692835646237507</v>
+        <v>0.01573322175455821</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.07395526494460926</v>
+        <v>0.03150864628911926</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1426729433185867</v>
+        <v>0.06078575620349066</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.322468886752618</v>
+        <v>0.1373886135857729</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.04388699714819143</v>
+        <v>0.01869803935562125</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2673886881361697</v>
+        <v>0.113921348768062</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.008904998181322253</v>
+        <v>0.003791690198275913</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2412424245286796</v>
+        <v>0.1027789065343242</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.007711409791431006</v>
+        <v>0.003282600089279196</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2477510599347071</v>
+        <v>0.105549060902897</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003767395534562574</v>
+        <v>0.001602240702793778</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2475664824886578</v>
+        <v>0.1054675513805128</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001795054320322797</v>
+        <v>0.0007620610095510659</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2473858851046422</v>
+        <v>0.1053877372774747</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0007448886434957832</v>
+        <v>0.0003145516565453449</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2470784298574016</v>
+        <v>0.105253898928402</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005151065842776062</v>
+        <v>0.000216469717637497</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2473625181820118</v>
+        <v>0.1053719973692969</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002121247269748935</v>
+        <v>8.713304438400528e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2472710956608187</v>
+        <v>0.1053301979607746</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001072528306660096</v>
+        <v>4.310835599971841e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2472739191829516</v>
+        <v>0.1053285406502816</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.908858326181952e-05</v>
+        <v>1.389510711220837e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2472445679491717</v>
+        <v>0.1053131658985331</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.905059697610734e-05</v>
+        <v>5.307398704046001e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2472435792146728</v>
+        <v>0.1053098645152194</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.858106375953874e-06</v>
+        <v>8.204558969451803e-08</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2472382096621457</v>
+        <v>0.1053047095517481</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.610817715762575e-07</v>
+        <v>-2.868697537608634e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.247232494590987</v>
+        <v>0.1052994176414942</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2472266996945082</v>
+        <v>0.1052940566389924</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.759791964848896e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2472214094524067</v>
+        <v>0.1052889120650587</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2472161215135562</v>
+        <v>0.1052837197793417</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2472108496795052</v>
+        <v>0.105283584270736</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2472108895349775</v>
+        <v>0.1052836241262082</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2472109293904498</v>
+        <v>0.1052836639816805</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2472109214193553</v>
+        <v>0.1052836560105861</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2472110808412444</v>
+        <v>0.1052838154324752</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.247210985188111</v>
+        <v>0.1052837197793417</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2472113359162672</v>
+        <v>0.105284070507498</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2472110888123389</v>
+        <v>0.1052838234035696</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2472110489568666</v>
+        <v>0.1052837835480974</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.247210985188111</v>
+        <v>0.1052837197793417</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2472110569279611</v>
+        <v>0.1052837915191918</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.247210985188111</v>
+        <v>0.1052837197793417</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2472110888123389</v>
+        <v>0.1052838234035696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2472111844654726</v>
+        <v>0.1052839190567033</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2472111206967167</v>
+        <v>0.1052838552879475</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-15.88973846592426</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2472110808412444</v>
+        <v>0.1052838154324752</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2472110569279611</v>
+        <v>0.1052837915191918</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2472108098240329</v>
+        <v>0.1052835444152637</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2472107301130881</v>
+        <v>0.1052834647043189</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2472107779396549</v>
+        <v>0.1052835125308856</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2472108975060719</v>
+        <v>0.1052836320973027</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.247210881563883</v>
+        <v>0.1052836161551138</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2472108975060719</v>
+        <v>0.1052836320973027</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.247210881563883</v>
+        <v>0.1052836161551138</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2472109373615442</v>
+        <v>0.105283671952775</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2472109373615442</v>
+        <v>0.105283671952775</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2472109373615442</v>
+        <v>0.105283671952775</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2472110888123389</v>
+        <v>0.1052838234035696</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2472113040318894</v>
+        <v>0.1052840386231202</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2472112163498504</v>
+        <v>0.1052839509410812</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2472111685232837</v>
+        <v>0.1052839031145144</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2472112163498504</v>
+        <v>0.1052839509410812</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2472110330146777</v>
+        <v>0.1052837676059084</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2472110409857722</v>
+        <v>0.1052837755770029</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2472110489568666</v>
+        <v>0.1052837835480974</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2472110569279611</v>
+        <v>0.1052837915191918</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2472110569279611</v>
+        <v>0.1052837915191918</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2472110967834333</v>
+        <v>0.1052838313746641</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2472111605521892</v>
+        <v>0.10528389514342</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2472112721475116</v>
+        <v>0.1052840067387423</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2472113199740783</v>
+        <v>0.1052840545653091</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.247211280118606</v>
+        <v>0.1052840147098368</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.247211208378756</v>
+        <v>0.1052839429699867</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2472113279451728</v>
+        <v>0.1052840625364035</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2472111685232837</v>
+        <v>0.1052839031145144</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2472109373615442</v>
+        <v>0.105283671952775</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2472108895349775</v>
+        <v>0.1052836241262082</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2472109214193553</v>
+        <v>0.1052836560105861</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.247210985188111</v>
+        <v>0.1052837197793417</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.247210985188111</v>
+        <v>0.1052837197793417</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2472109054771664</v>
+        <v>0.1052836400683972</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2472107859107494</v>
+        <v>0.1052835205019801</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2472107460552771</v>
+        <v>0.1052834806465078</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2472108895349775</v>
+        <v>0.1052836241262082</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2472110250435832</v>
+        <v>0.105283759634814</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2472110091013943</v>
+        <v>0.1052837436926251</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.247210985188111</v>
+        <v>0.1052837197793417</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2472109453326387</v>
+        <v>0.1052836799238694</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2472108417084108</v>
+        <v>0.1052835762996415</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2472107221419937</v>
+        <v>0.1052834567332245</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2472108417084108</v>
+        <v>0.1052835762996415</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2472108895349775</v>
+        <v>0.1052836241262082</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.247210985188111</v>
+        <v>0.1052837197793417</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2472108656216941</v>
+        <v>0.1052836002129249</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.7769695850834732</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2472108735927886</v>
+        <v>0.1052836081840193</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000001.xlsx
+++ b/out/Attention-S4_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC43" t="n">
-        <v>-8.576601622242015e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03692835646237507</v>
+        <v>0</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.07395526494460926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1426729433185867</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.322468886752618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.04388699714819143</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2673886881361697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.008904998181322253</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2412424245286796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.007711409791431006</v>
+        <v>0</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2477510599347071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003767395534562574</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2475664824886578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001795054320322797</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2473858851046422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0007448886434957832</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2470784298574016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005151065842776062</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2473625181820118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002121247269748935</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2472710956608187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001072528306660096</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2472739191829516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.908858326181952e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2472445679491717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.905059697610734e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2472435792146728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.858106375953874e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2472382096621457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.610817715762575e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.247232494590987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2472266996945082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.759791964848896e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2472214094524067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2472161215135562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2472108496795052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2472108895349775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2472109293904498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2472109214193553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2472110808412444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.247210985188111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2472113359162672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2472110888123389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2472110489568666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.247210985188111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2472110569279611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.247210985188111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2472110888123389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2472111844654726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.9425263098030442</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2472111206967167</v>
+        <v>-1.108987994515337e-05</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-1.785820764982441e-05</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-15.88973846592426</v>
+        <v>-0.9425263098030442</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2472110808412444</v>
+        <v>-0.0009452652513548965</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0</v>
+        <v>-5.245870272047919e-05</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.9425263098030442</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2472110569279611</v>
+        <v>-0.001500835523167974</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>0</v>
+        <v>-0.006941832531516965</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2472108098240329</v>
+        <v>-0.007023239321832428</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2472107301130881</v>
+        <v>-0.007023239321832428</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2472107779396549</v>
+        <v>-0.007146316477835644</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0</v>
+        <v>0.02394470489250804</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2472108975060719</v>
+        <v>0.04096407650366635</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0</v>
+        <v>0.01036373110160104</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.247210881563883</v>
+        <v>0.03763396950028476</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0</v>
+        <v>0.005986235459940854</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2472108975060719</v>
+        <v>0.03918980689006694</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0</v>
+        <v>0.002590958414238274</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.247210881563883</v>
+        <v>0.03835727588645532</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0</v>
+        <v>0.001997169868643801</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2472109373615442</v>
+        <v>0.03975030056371388</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0</v>
+        <v>0.0009960849343219002</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2472109373615442</v>
+        <v>0.03973947684572707</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0</v>
+        <v>0.0004955424671609502</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2472109373615442</v>
+        <v>0.0397315649867336</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0</v>
+        <v>0.0004841250695379043</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2472110888123389</v>
+        <v>0.04020310369811766</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0</v>
+        <v>0.0004090121057579344</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2472113040318894</v>
+        <v>0.0405368607010697</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0</v>
+        <v>0.000167675573818636</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2472112163498504</v>
+        <v>0.04046209543685825</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0</v>
+        <v>7.170868278112412e-05</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2472111685232837</v>
+        <v>0.04043796765093529</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0</v>
+        <v>3.827818179251889e-05</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2472112163498504</v>
+        <v>0.04044231288360735</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0</v>
+        <v>7.447870871183987e-06</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2472110330146777</v>
+        <v>0.04041911189627612</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0</v>
+        <v>1.549992754804508e-06</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2472110409857722</v>
+        <v>0.04041448429082369</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0</v>
+        <v>-1.760465127922526e-06</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2472110489568666</v>
+        <v>0.04040967089651711</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>0</v>
+        <v>-3.332463389075608e-06</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2472110569279611</v>
+        <v>0.04040476812751929</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>0</v>
+        <v>-4.166231694537805e-06</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2472110569279611</v>
+        <v>0.04039976493090636</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0</v>
+        <v>-4.364539171549108e-06</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2472110967834333</v>
+        <v>0.0403949221260671</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>0</v>
+        <v>-4.618577352593679e-06</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2472111605521892</v>
+        <v>0.0403900484736918</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2472112721475116</v>
+        <v>0.0403901600690143</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2472113199740783</v>
+        <v>0.04039020789558103</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.247211280118606</v>
+        <v>0.04039016804010875</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.247211208378756</v>
+        <v>0.04039009630025853</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2472113279451728</v>
+        <v>0.04039021586667548</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2472111685232837</v>
+        <v>0.04039005644478626</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2472109373615442</v>
+        <v>0.04038982528304693</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2472108895349775</v>
+        <v>0.04038977745648008</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2472109214193553</v>
+        <v>0.04038980934085801</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.247210985188111</v>
+        <v>0.04038987310961367</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.247210985188111</v>
+        <v>0.04038987310961367</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2472109054771664</v>
+        <v>0.0403897933986691</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2472107859107494</v>
+        <v>0.04038967383225216</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2472107460552771</v>
+        <v>0.04038963397677988</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2472108895349775</v>
+        <v>0.04038977745648008</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2472110250435832</v>
+        <v>0.04038991296508594</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2472110091013943</v>
+        <v>0.04038989702289703</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.247210985188111</v>
+        <v>0.04038987310961367</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2472109453326387</v>
+        <v>0.04038983325414138</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2472108417084108</v>
+        <v>0.04038972962991334</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0</v>
+        <v>-5.056461455712194e-06</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2472107221419937</v>
+        <v>0.04038460939970193</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2472108417084108</v>
+        <v>0.04038460939970193</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2472108895349775</v>
+        <v>0.04038460939970193</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.247210985188111</v>
+        <v>0.04038460939970193</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2472108656216941</v>
+        <v>0.04038460939970193</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.79359707945414e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2472108735927886</v>
+        <v>0.04038460939970193</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000001.xlsx
+++ b/out/Attention-S4_repeat_1_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.00367150641977787</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.009915471076965332</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.005129406228661537</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.003935022279620171</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.006367016583681107</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.01057866774499416</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.004009228199720383</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.003580834716558456</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.007329218089580536</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001761972904205322</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.006270511075854301</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.003334216773509979</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.007570169866085052</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01000611484050751</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.009872737340629101</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.009723932482302189</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.007299022749066353</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.007192502729594707</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.006067340262234211</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002325363457202911</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.003361145965754986</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.005515947937965393</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.008548554033041</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.008356519043445587</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.005622571334242821</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.005752969533205032</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.005427151918411255</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002236807718873024</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.006015687249600887</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.008887277916073799</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.003851523622870445</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.008504166267812252</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.003327138721942902</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.003987390547990799</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.001573516055941582</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.00654430128633976</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.007941278629004955</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.008747854270040989</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01169522292912006</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01347094122320414</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01497669517993927</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01682913303375244</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0184498243033886</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.008660690858960152</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.002743941266089678</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.007368813268840313</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.003381453454494476</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01002873480319977</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01272417325526476</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01590483635663986</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01568522490561008</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01667650230228901</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01170224696397781</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.009979963302612305</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.008459953591227531</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.004164407029747963</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.006930647417902946</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.008599435910582542</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.008946986868977547</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01179093681275845</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.009370440617203712</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01091471873223782</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.009355315938591957</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.009736953303217888</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01251864619553089</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01372713409364223</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01290961354970932</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01749310828745365</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01696724817156792</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.006275301799178123</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01096233725547791</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.008493052795529366</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.00635589100420475</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.001089397817850113</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.004090422764420509</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9425263098030442</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>-1.108987994515337e-05</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.785820764982441e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.002823261544108391</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9425263098030442</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.0009452652513548965</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-5.245870272047919e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.008729482069611549</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9425263098030442</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.001500835523167974</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-0.006941832531516965</v>
+        <v>0</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.004162071272730827</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.007023239321832428</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.006599707528948784</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.007023239321832428</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0100079532712698</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.007146316477835644</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.02394470489250804</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.006722526624798775</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.04096407650366635</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.01036373110160104</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.006798563525080681</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.03763396950028476</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.005986235459940854</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.001232685521245003</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.03918980689006694</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.002590958414238274</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.004321826621890068</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.03835727588645532</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.001997169868643801</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.006950555369257927</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.03975030056371388</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.0009960849343219002</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.00300273485481739</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2462105352954338</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.03973947684572707</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.0004955424671609502</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.00944121740758419</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.0397315649867336</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0004841250695379043</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01001660339534283</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.04020310369811766</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.0004090121057579344</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01048035360872746</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.0405368607010697</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.000167675573818636</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.008365264162421227</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.04046209543685825</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>7.170868278112412e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.009461941197514534</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.04043796765093529</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>3.827818179251889e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.009473523125052452</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.04044231288360735</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>7.447870871183987e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.007818842306733131</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.04041911189627612</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>1.549992754804508e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.009494272992014885</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.04041448429082369</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-1.760465127922526e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01241734810173512</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.04040967089651711</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-3.332463389075608e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.007844218984246254</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.04040476812751929</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-4.166231694537805e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.002314506098628044</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.04039976493090636</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-4.364539171549108e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01739508472383022</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.0403949221260671</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-4.618577352593679e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01235376857221127</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.0403900484736918</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01232533343136311</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.0403901600690143</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.008254291489720345</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.04039020789558103</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01055959425866604</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.04039016804010875</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.006015704944729805</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.04039009630025853</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.009612126275897026</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.04039021586667548</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01385796256363392</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.04039005644478626</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.006552891805768013</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.04038982528304693</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.007336067035794258</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.04038977745648008</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.001448502764105797</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.04038980934085801</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.01076111383736134</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.04038987310961367</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.00943283922970295</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.04038987310961367</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.009953996166586876</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.0403897933986691</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.007686598226428032</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.04038967383225216</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.003324201330542564</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.04038963397677988</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.002483630552887917</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.04038977745648008</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.003324097022414207</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.04038991296508594</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.003129592165350914</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.04038989702289703</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.005956592038273811</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.04038987310961367</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.004404431208968163</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.04038983325414138</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.009997112676501274</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.04038972962991334</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-5.056461455712194e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.01087152399122715</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.04038460939970193</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.00343720056116581</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.04038460939970193</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.006191888824105263</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.04038460939970193</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>3.972090780735016e-05</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.04038460939970193</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.002362726256251335</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999995</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.04038460939970193</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.009947419166564941</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.04038460939970193</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>
